--- a/EX2/CPa_effectivenes_pre_vs_post_calibration/Aggregated_Platt_CP_with_LApredict_test_set.xlsx
+++ b/EX2/CPa_effectivenes_pre_vs_post_calibration/Aggregated_Platt_CP_with_LApredict_test_set.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX2\CPa_effectivenes_pre_vs_post_calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9DDC96-2A9B-4097-AF5A-2E973743639B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48811196-F1CA-4096-ABE4-0A1A3D7A1936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="444" windowWidth="24912" windowHeight="14112" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OS_alpha_0.05" sheetId="1" r:id="rId1"/>
@@ -1260,7 +1260,7 @@
         <v>0.89430591737997767</v>
       </c>
       <c r="O2" s="5">
-        <f>F2/3701</f>
+        <f t="shared" ref="O2:O11" si="0">F2/3701</f>
         <v>0.64928397730343146</v>
       </c>
     </row>
@@ -1301,11 +1301,11 @@
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="3">
-        <f t="shared" ref="N3:N11" si="0">F3/D3</f>
+        <f t="shared" ref="N3:N11" si="1">F3/D3</f>
         <v>0.89678638941398869</v>
       </c>
       <c r="O3" s="5">
-        <f t="shared" ref="O3:O11" si="1">F3/3701</f>
+        <f t="shared" si="0"/>
         <v>0.64090786273980005</v>
       </c>
     </row>
@@ -1346,11 +1346,11 @@
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.89249639249639245</v>
       </c>
       <c r="O4" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.66846798162658738</v>
       </c>
     </row>
@@ -1391,11 +1391,11 @@
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.89250567751703258</v>
       </c>
       <c r="O5" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.63712510132396649</v>
       </c>
     </row>
@@ -1436,11 +1436,11 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.88773747841105355</v>
       </c>
       <c r="O6" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.69440691704944613</v>
       </c>
     </row>
@@ -1481,11 +1481,11 @@
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.89405204460966547</v>
       </c>
       <c r="O7" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.64982437179140773</v>
       </c>
     </row>
@@ -1526,11 +1526,11 @@
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.88718510405257389</v>
       </c>
       <c r="O8" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.65657930289111055</v>
       </c>
     </row>
@@ -1571,11 +1571,11 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.88931165686613634</v>
       </c>
       <c r="O9" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.69467711429343426</v>
       </c>
     </row>
@@ -1616,11 +1616,11 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.88829988640666413</v>
       </c>
       <c r="O10" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.6338827343961092</v>
       </c>
     </row>
@@ -1661,11 +1661,11 @@
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.88142019993105825</v>
       </c>
       <c r="O11" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.6908943528776007</v>
       </c>
     </row>

--- a/EX2/CPa_effectivenes_pre_vs_post_calibration/Aggregated_Platt_CP_with_LApredict_test_set.xlsx
+++ b/EX2/CPa_effectivenes_pre_vs_post_calibration/Aggregated_Platt_CP_with_LApredict_test_set.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX2\CPa_effectivenes_pre_vs_post_calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48811196-F1CA-4096-ABE4-0A1A3D7A1936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA01EC98-A2EE-434D-9D26-41D876030376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36315" yWindow="2595" windowWidth="23430" windowHeight="11475" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OS_alpha_0.05" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="69">
   <si>
     <t>nr_instances</t>
   </si>
@@ -169,15 +169,9 @@
     <t>0.893233743</t>
   </si>
   <si>
-    <t>0.943759147</t>
-  </si>
-  <si>
     <t>0.925151579</t>
   </si>
   <si>
-    <t>0.947313402</t>
-  </si>
-  <si>
     <t>0.954421911</t>
   </si>
   <si>
@@ -190,24 +184,15 @@
     <t>0.945640811</t>
   </si>
   <si>
-    <t>0.964457453</t>
-  </si>
-  <si>
     <t>0.960275977</t>
   </si>
   <si>
-    <t>0.952958394</t>
-  </si>
-  <si>
     <t>0.90048087</t>
   </si>
   <si>
     <t>0.889399958</t>
   </si>
   <si>
-    <t>0.898181058</t>
-  </si>
-  <si>
     <t>0.914070667</t>
   </si>
   <si>
@@ -217,18 +202,9 @@
     <t>0.895044951</t>
   </si>
   <si>
-    <t>0.890863475</t>
-  </si>
-  <si>
     <t>0.907171231</t>
   </si>
   <si>
-    <t>0.902989755</t>
-  </si>
-  <si>
-    <t>0.855111854</t>
-  </si>
-  <si>
     <t>0.859711478</t>
   </si>
   <si>
@@ -238,9 +214,6 @@
     <t>0.843612795</t>
   </si>
   <si>
-    <t>0.854066485</t>
-  </si>
-  <si>
     <t>0.832740958</t>
   </si>
   <si>
@@ -260,17 +233,36 @@
   </si>
   <si>
     <t>Platt-scaled LApredict with openstack makes 4089 correct predictions (23 fault-prone ; 4067 clean)</t>
+  </si>
+  <si>
+    <t>Precision_clean</t>
+  </si>
+  <si>
+    <t>recall_clean</t>
+  </si>
+  <si>
+    <t>Precision faulty</t>
+  </si>
+  <si>
+    <t>recall_faulty</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -331,23 +323,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -577,13 +573,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="14" max="15" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -623,8 +619,20 @@
       <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>4552</v>
       </c>
@@ -668,8 +676,24 @@
         <f>F2/3701</f>
         <v>0.42420967306133478</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>I2/(I2+J2)</f>
+        <v>0.91612522150029529</v>
+      </c>
+      <c r="R2">
+        <f>I2/3504</f>
+        <v>0.44263698630136988</v>
+      </c>
+      <c r="T2">
+        <f>H2/(H2+K2)</f>
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="U2">
+        <f>H2/197</f>
+        <v>9.6446700507614211E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>4552</v>
       </c>
@@ -713,8 +737,24 @@
         <f t="shared" ref="O3:O11" si="1">F3/3701</f>
         <v>0.42447987030532286</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">I3/(I3+J3)</f>
+        <v>0.91637010676156583</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">I3/3504</f>
+        <v>0.44092465753424659</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">H3/(H3+K3)</f>
+        <v>0.78787878787878785</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">H3/197</f>
+        <v>0.13197969543147209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>4552</v>
       </c>
@@ -758,8 +798,24 @@
         <f t="shared" si="1"/>
         <v>0.42907322345312077</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.91540256709451573</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.44777397260273971</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>9.6446700507614211E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4552</v>
       </c>
@@ -803,8 +859,24 @@
         <f t="shared" si="1"/>
         <v>0.42529046203728721</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.91646778042959431</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.43835616438356162</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.19289340101522842</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>4552</v>
       </c>
@@ -848,8 +920,24 @@
         <f t="shared" si="1"/>
         <v>0.49392056201026752</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.9134419551934827</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.51198630136986301</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.17258883248730963</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>4552</v>
       </c>
@@ -893,8 +981,24 @@
         <f t="shared" si="1"/>
         <v>0.45960551202377736</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.91534680502457677</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.47831050228310501</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.78125</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.12690355329949238</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>4552</v>
       </c>
@@ -938,8 +1042,24 @@
         <f t="shared" si="1"/>
         <v>0.51121318562550666</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.91323748140803174</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.52568493150684936</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.70422535211267601</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.25380710659898476</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>4552</v>
       </c>
@@ -983,8 +1103,24 @@
         <f t="shared" si="1"/>
         <v>0.441772493920562</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.91543700340522138</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.4603310502283105</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.1116751269035533</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>4552</v>
       </c>
@@ -1028,8 +1164,24 @@
         <f t="shared" si="1"/>
         <v>0.441772493920562</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.91459896133871899</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.45234018264840181</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.70422535211267601</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.25380710659898476</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>4552</v>
       </c>
@@ -1073,8 +1225,24 @@
         <f t="shared" si="1"/>
         <v>0.47014320453931369</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0.91576086956521741</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>0.48087899543378998</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.70512820512820518</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.27918781725888325</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="D12" s="6">
         <f>AVERAGE(D2:D11)</f>
         <v>1836.7</v>
@@ -1102,16 +1270,24 @@
       <c r="P12" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H13">
-        <f>H12+J13</f>
-        <v>185.8</v>
-      </c>
-      <c r="I13">
-        <f>I12+K13</f>
-        <v>1650.8999999999999</v>
-      </c>
+      <c r="Q12" s="6">
+        <f t="shared" ref="Q12:R12" si="6">AVERAGE(Q2:Q11)</f>
+        <v>0.91521887517212197</v>
+      </c>
+      <c r="R12" s="6">
+        <f t="shared" si="6"/>
+        <v>0.4679223744292238</v>
+      </c>
+      <c r="T12" s="6">
+        <f t="shared" ref="T12:U12" si="7">AVERAGE(T2:T11)</f>
+        <v>0.76529457924704403</v>
+      </c>
+      <c r="U12" s="6">
+        <f t="shared" si="7"/>
+        <v>0.17157360406091374</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="J13" s="6">
         <f>AVERAGE(J2:J11)</f>
         <v>152</v>
@@ -1132,7 +1308,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="N14" s="5">
         <f>MIN(N2:N11)</f>
         <v>0.9061302681992337</v>
@@ -1145,7 +1321,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="N15" s="5">
         <f>MAX(N2:N11)</f>
         <v>0.91438555620267914</v>
@@ -1160,7 +1336,7 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1171,14 +1347,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298A91B4-BE41-4671-A010-BAAC415A75D1}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1218,8 +1394,20 @@
       <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>4552</v>
       </c>
@@ -1263,8 +1451,24 @@
         <f t="shared" ref="O2:O11" si="0">F2/3701</f>
         <v>0.64928397730343146</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>I2/(I2+J2)</f>
+        <v>0.89577039274924475</v>
+      </c>
+      <c r="R2">
+        <f>I2/3504</f>
+        <v>0.6769406392694064</v>
+      </c>
+      <c r="T2">
+        <f>H2/(H2+K2)</f>
+        <v>0.79487179487179482</v>
+      </c>
+      <c r="U2">
+        <f>H2/197</f>
+        <v>0.15736040609137056</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>4552</v>
       </c>
@@ -1308,8 +1512,24 @@
         <f t="shared" si="0"/>
         <v>0.64090786273980005</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">I3/(I3+J3)</f>
+        <v>0.89899768696993065</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">I3/3504</f>
+        <v>0.66552511415525117</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">H3/(H3+K3)</f>
+        <v>0.78431372549019607</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">H3/197</f>
+        <v>0.20304568527918782</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>4552</v>
       </c>
@@ -1353,8 +1573,24 @@
         <f t="shared" si="0"/>
         <v>0.66846798162658738</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.89388949871935597</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.69720319634703198</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.79487179487179482</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0.15736040609137056</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4552</v>
       </c>
@@ -1398,8 +1634,24 @@
         <f t="shared" si="0"/>
         <v>0.63712510132396649</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.89816621147093245</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.65696347031963476</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.70886075949367089</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.28426395939086296</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>4552</v>
       </c>
@@ -1443,8 +1695,24 @@
         <f t="shared" si="0"/>
         <v>0.69440691704944613</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.89262934089298374</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.71889269406392697</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.69863013698630139</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.25888324873096447</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>4552</v>
       </c>
@@ -1488,8 +1756,24 @@
         <f t="shared" si="0"/>
         <v>0.64982437179140773</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.89617279272451689</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.67494292237442921</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.78431372549019607</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.20304568527918782</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>4552</v>
       </c>
@@ -1533,8 +1817,24 @@
         <f t="shared" si="0"/>
         <v>0.65657930289111055</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.89736741701640599</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.67123287671232879</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.66101694915254239</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.39593908629441626</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>4552</v>
       </c>
@@ -1578,8 +1878,24 @@
         <f t="shared" si="0"/>
         <v>0.69467711429343426</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.89119718309859153</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.72231735159817356</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.78431372549019607</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.20304568527918782</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>4552</v>
       </c>
@@ -1623,8 +1939,24 @@
         <f t="shared" si="0"/>
         <v>0.6338827343961092</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.8994413407821229</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.6432648401826484</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.68148148148148147</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.46700507614213199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>4552</v>
       </c>
@@ -1668,8 +2000,24 @@
         <f t="shared" si="0"/>
         <v>0.6908943528776007</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0.8941991973732214</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>0.69948630136986301</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.66249999999999998</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.53807106598984766</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="D12" s="6">
         <f>AVERAGE(D2:D11)</f>
         <v>2750.3</v>
@@ -1697,15 +2045,27 @@
       <c r="P12" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H13">
-        <f>H12+J13</f>
-        <v>335.1</v>
-      </c>
+      <c r="Q12" s="6">
+        <f t="shared" ref="Q12:R12" si="6">AVERAGE(Q2:Q11)</f>
+        <v>0.89578310617973078</v>
+      </c>
+      <c r="R12" s="6">
+        <f t="shared" si="6"/>
+        <v>0.68267694063926931</v>
+      </c>
+      <c r="T12" s="6">
+        <f t="shared" ref="T12:U12" si="7">AVERAGE(T2:T11)</f>
+        <v>0.7355174093328174</v>
+      </c>
+      <c r="U12" s="6">
+        <f t="shared" si="7"/>
+        <v>0.28680203045685276</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="I13">
-        <f>I12+K13</f>
-        <v>2415.1999999999998</v>
+        <f>I12+J13</f>
+        <v>2670.7</v>
       </c>
       <c r="J13" s="6">
         <f>AVERAGE(J2:J11)</f>
@@ -1727,7 +2087,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="N14" s="5">
         <f>MIN(N2:N11)</f>
         <v>0.88142019993105825</v>
@@ -1740,7 +2100,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="N15" s="5">
         <f>MAX(N2:N11)</f>
         <v>0.89678638941398869</v>
@@ -1760,14 +2120,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{285A6E10-CCB5-4281-A2FA-CB15A328DD34}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1807,8 +2167,20 @@
       <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>4552</v>
       </c>
@@ -1852,8 +2224,24 @@
         <f>F2/3701</f>
         <v>0.80221561740070246</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>I2/(I2+J2)</f>
+        <v>0.87354607813898</v>
+      </c>
+      <c r="R2">
+        <f>I2/3504</f>
+        <v>0.83590182648401823</v>
+      </c>
+      <c r="T2">
+        <f>H2/(H2+K2)</f>
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="U2">
+        <f>H2/197</f>
+        <v>0.20304568527918782</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>4552</v>
       </c>
@@ -1897,8 +2285,24 @@
         <f t="shared" ref="O3:O11" si="1">F3/3701</f>
         <v>0.82112942447987025</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">I3/(I3+J3)</f>
+        <v>0.87016412661195774</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">I3/3504</f>
+        <v>0.84731735159817356</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">H3/(H3+K3)</f>
+        <v>0.67961165048543692</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">H3/197</f>
+        <v>0.35532994923857869</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>4552</v>
       </c>
@@ -1942,8 +2346,24 @@
         <f t="shared" si="1"/>
         <v>0.82464198865171578</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.86899942163100052</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.85759132420091322</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.72307692307692306</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0.23857868020304568</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4552</v>
       </c>
@@ -1987,8 +2407,24 @@
         <f t="shared" si="1"/>
         <v>0.83896244258308561</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.86945169712793735</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.8553082191780822</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.54822335025380708</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>4552</v>
       </c>
@@ -2032,8 +2468,24 @@
         <f t="shared" si="1"/>
         <v>0.83085652526344234</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.86961583236321305</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.85273972602739723</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.6796875</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.44162436548223349</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>4552</v>
       </c>
@@ -2077,8 +2529,24 @@
         <f t="shared" si="1"/>
         <v>0.82437179140772765</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.86969168121000584</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.85331050228310501</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.67032967032967028</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.30964467005076141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>4552</v>
       </c>
@@ -2122,8 +2590,24 @@
         <f t="shared" si="1"/>
         <v>0.79383950283707105</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.87995010913626437</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.80536529680365299</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.65536723163841804</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.58883248730964466</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>4552</v>
       </c>
@@ -2167,8 +2651,24 @@
         <f t="shared" si="1"/>
         <v>0.8594974331261821</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.86460939671948844</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.88755707762557079</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.66355140186915884</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.3604060913705584</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>4552</v>
       </c>
@@ -2212,8 +2712,24 @@
         <f t="shared" si="1"/>
         <v>0.78114023236962982</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.88096753660089111</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.78995433789954339</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.63076923076923075</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.62436548223350252</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>4552</v>
       </c>
@@ -2257,8 +2773,24 @@
         <f t="shared" si="1"/>
         <v>0.81113212645231014</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0.87825820300521318</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>0.81735159817351599</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.60792951541850215</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.70050761421319796</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="D12" s="6">
         <f>AVERAGE(D2:D11)</f>
         <v>3505.8</v>
@@ -2286,16 +2818,24 @@
       <c r="P12" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H13">
-        <f>H12+J13</f>
-        <v>517</v>
-      </c>
-      <c r="I13">
-        <f>I12+K13</f>
-        <v>2988.7999999999997</v>
-      </c>
+      <c r="Q12" s="6">
+        <f t="shared" ref="Q12:R12" si="6">AVERAGE(Q2:Q11)</f>
+        <v>0.87252540825449521</v>
+      </c>
+      <c r="R12" s="6">
+        <f t="shared" si="6"/>
+        <v>0.84023972602739738</v>
+      </c>
+      <c r="T12" s="6">
+        <f t="shared" ref="T12:U12" si="7">AVERAGE(T2:T11)</f>
+        <v>0.67462205594847746</v>
+      </c>
+      <c r="U12" s="6">
+        <f t="shared" si="7"/>
+        <v>0.43705583756345179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="J13" s="6">
         <f>AVERAGE(J2:J11)</f>
         <v>430.9</v>
@@ -2316,7 +2856,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="N14" s="5">
         <f>MIN(N2:N11)</f>
         <v>0.85880129589632825</v>
@@ -2329,7 +2869,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="N15" s="5">
         <f>MAX(N2:N11)</f>
         <v>0.87195301027900152</v>
@@ -2349,13 +2889,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DB74A44-7E98-4787-AD64-665D6EB42FFE}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="14" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2395,56 +2935,84 @@
       <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+      <c r="Q1" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>4783</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3">
-        <v>2803</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1980</v>
-      </c>
-      <c r="F2" s="3">
-        <v>2534</v>
-      </c>
-      <c r="G2" s="3">
-        <v>269</v>
-      </c>
-      <c r="H2" s="3">
-        <v>6</v>
-      </c>
-      <c r="I2" s="3">
-        <v>2528</v>
-      </c>
-      <c r="J2" s="3">
-        <v>264</v>
-      </c>
-      <c r="K2" s="3">
-        <v>5</v>
+      <c r="B2">
+        <v>0.95295839431319251</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>2525</v>
+      </c>
+      <c r="E2">
+        <v>2258</v>
+      </c>
+      <c r="F2">
+        <v>2300</v>
+      </c>
+      <c r="G2">
+        <v>225</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2298</v>
+      </c>
+      <c r="J2">
+        <v>222</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
       </c>
       <c r="N2" s="3">
         <f>F2/D2</f>
-        <v>0.90403139493399931</v>
+        <v>0.91089108910891092</v>
       </c>
       <c r="O2" s="5">
         <f>F2/4089</f>
-        <v>0.61971142088530207</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.5624847150892639</v>
+      </c>
+      <c r="Q2">
+        <f>I2/(I2+J2)</f>
+        <v>0.91190476190476188</v>
+      </c>
+      <c r="R2">
+        <f>I2/4067</f>
+        <v>0.56503565281534296</v>
+      </c>
+      <c r="T2">
+        <f>H2/(H2+K2)</f>
+        <v>0.4</v>
+      </c>
+      <c r="U2">
+        <f>H2/23</f>
+        <v>8.6956521739130432E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>4783</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3">
         <v>0</v>
@@ -2481,56 +3049,88 @@
         <f t="shared" ref="O3:O11" si="1">F3/4089</f>
         <v>0.75544142822205917</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">I3/(I3+J3)</f>
+        <v>0.89689224513505661</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">I3/4067</f>
+        <v>0.75928202606343742</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">H3/(H3+K3)</f>
+        <v>0.25</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">H3/23</f>
+        <v>4.3478260869565216E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>4783</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2686</v>
-      </c>
-      <c r="E4" s="3">
-        <v>2097</v>
-      </c>
-      <c r="F4" s="3">
-        <v>2434</v>
-      </c>
-      <c r="G4" s="3">
-        <v>252</v>
-      </c>
-      <c r="H4" s="3">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3">
-        <v>2433</v>
-      </c>
-      <c r="J4" s="3">
-        <v>249</v>
-      </c>
-      <c r="K4" s="3">
-        <v>3</v>
+      <c r="B4">
+        <v>0.96090319882918673</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>2272</v>
+      </c>
+      <c r="E4">
+        <v>2511</v>
+      </c>
+      <c r="F4">
+        <v>2085</v>
+      </c>
+      <c r="G4">
+        <v>187</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>2085</v>
+      </c>
+      <c r="J4">
+        <v>185</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
       </c>
       <c r="N4" s="3">
         <f t="shared" si="0"/>
-        <v>0.90618019359642588</v>
+        <v>0.917693661971831</v>
       </c>
       <c r="O4" s="5">
         <f t="shared" si="1"/>
-        <v>0.59525556370750798</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.5099046221570066</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.91850220264317184</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.51266289648389474</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4783</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C5" s="3">
         <v>0</v>
@@ -2557,7 +3157,7 @@
         <v>216</v>
       </c>
       <c r="K5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N5" s="3">
         <f t="shared" si="0"/>
@@ -2567,13 +3167,29 @@
         <f t="shared" si="1"/>
         <v>0.55661530936659331</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.913322632423756</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.5596262601426113</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>4783</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C6" s="3">
         <v>0</v>
@@ -2610,13 +3226,29 @@
         <f t="shared" si="1"/>
         <v>0.60259232086084613</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.90584773813902175</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.60560609786083108</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>4783</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C7" s="3">
         <v>0</v>
@@ -2653,13 +3285,29 @@
         <f t="shared" si="1"/>
         <v>0.52971386647101981</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.91582064297800336</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.53233341529382838</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>4783</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C8" s="3">
         <v>0</v>
@@ -2696,56 +3344,88 @@
         <f t="shared" si="1"/>
         <v>0.60503790657862555</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.90586080586080586</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.60806491271207275</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>4783</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="3">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3">
-        <v>2117</v>
-      </c>
-      <c r="E9" s="3">
-        <v>2666</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1947</v>
-      </c>
-      <c r="G9" s="3">
-        <v>170</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1946</v>
-      </c>
-      <c r="J9" s="3">
-        <v>168</v>
-      </c>
-      <c r="K9" s="3">
-        <v>2</v>
+      <c r="B9">
+        <v>0.94794062303993309</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>2678</v>
+      </c>
+      <c r="E9">
+        <v>2105</v>
+      </c>
+      <c r="F9">
+        <v>2429</v>
+      </c>
+      <c r="G9">
+        <v>249</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>2429</v>
+      </c>
+      <c r="J9">
+        <v>248</v>
+      </c>
+      <c r="K9">
+        <v>5</v>
       </c>
       <c r="N9" s="3">
         <f t="shared" si="0"/>
-        <v>0.91969768540387342</v>
+        <v>0.90702016430171772</v>
       </c>
       <c r="O9" s="5">
         <f t="shared" si="1"/>
-        <v>0.47615553925165077</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.59403277084861827</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.90735898393724324</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.59724612736660931</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>4783</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C10" s="3">
         <v>0</v>
@@ -2782,125 +3462,169 @@
         <f t="shared" si="1"/>
         <v>0.51283932501834184</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.91845681718544503</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.51512171133513651</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>8.6956521739130432E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>4783</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="3">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3">
-        <v>2525</v>
-      </c>
-      <c r="E11" s="3">
-        <v>2258</v>
-      </c>
-      <c r="F11" s="3">
-        <v>2300</v>
-      </c>
-      <c r="G11" s="3">
-        <v>225</v>
-      </c>
-      <c r="H11" s="3">
-        <v>2</v>
-      </c>
-      <c r="I11" s="3">
-        <v>2298</v>
-      </c>
-      <c r="J11" s="3">
-        <v>222</v>
-      </c>
-      <c r="K11" s="3">
+      <c r="B11">
+        <v>0.94731340163077571</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>2686</v>
+      </c>
+      <c r="E11">
+        <v>2097</v>
+      </c>
+      <c r="F11">
+        <v>2434</v>
+      </c>
+      <c r="G11">
+        <v>252</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>2433</v>
+      </c>
+      <c r="J11">
+        <v>249</v>
+      </c>
+      <c r="K11">
         <v>3</v>
       </c>
       <c r="N11" s="3">
         <f t="shared" si="0"/>
-        <v>0.91089108910891092</v>
+        <v>0.90618019359642588</v>
       </c>
       <c r="O11" s="5">
         <f t="shared" si="1"/>
-        <v>0.5624847150892639</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.59525556370750798</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0.90715883668903807</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>0.59822965330710598</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="D12" s="6">
         <f>AVERAGE(D2:D11)</f>
-        <v>2618.3000000000002</v>
+        <v>2621.3000000000002</v>
       </c>
       <c r="F12" s="6">
         <f>AVERAGE(F2:F11)</f>
-        <v>2378.1</v>
+        <v>2381.4</v>
       </c>
       <c r="H12" s="6">
         <f>AVERAGE(H2:H11)</f>
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="I12" s="6">
         <f>AVERAGE(I2:I11)</f>
-        <v>2376.5</v>
+        <v>2380.5</v>
       </c>
       <c r="N12" s="6">
         <f>AVERAGE(N2:N11)</f>
-        <v>0.90913218285988351</v>
+        <v>0.909230657453451</v>
       </c>
       <c r="O12" s="6">
         <f>AVERAGE(O2:O11)</f>
-        <v>0.58158473954512102</v>
+        <v>0.58239178283198823</v>
       </c>
       <c r="P12" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H13">
-        <f>H12+J13</f>
-        <v>238.79999999999998</v>
-      </c>
+      <c r="Q12" s="6">
+        <f t="shared" ref="Q12:R12" si="6">AVERAGE(Q2:Q11)</f>
+        <v>0.91011256668963048</v>
+      </c>
+      <c r="R12" s="6">
+        <f t="shared" si="6"/>
+        <v>0.58532087533808697</v>
+      </c>
+      <c r="T12" s="6">
+        <f t="shared" ref="T12:U12" si="7">AVERAGE(T2:T11)</f>
+        <v>0.20666666666666664</v>
+      </c>
+      <c r="U12" s="6">
+        <f t="shared" si="7"/>
+        <v>3.9130434782608692E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="I13">
-        <f>I12+K13</f>
-        <v>2379.5</v>
+        <f>I12+J13</f>
+        <v>2617.8000000000002</v>
       </c>
       <c r="J13" s="6">
         <f>AVERAGE(J2:J11)</f>
-        <v>237.2</v>
+        <v>237.3</v>
       </c>
       <c r="K13" s="6">
         <f>AVERAGE(K2:K11)</f>
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N13" s="5">
         <f>STDEV(N2:N11)</f>
-        <v>7.1662556033969642E-3</v>
+        <v>6.6850718221491169E-3</v>
       </c>
       <c r="O13" s="5">
         <f>STDEV(O2:O11)</f>
-        <v>7.6287593371506326E-2</v>
+        <v>7.0785820567436764E-2</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="N14" s="5">
         <f>MIN(N2:N11)</f>
         <v>0.89614157238178127</v>
       </c>
       <c r="O14" s="5">
         <f>MIN(O2:O11)</f>
-        <v>0.47615553925165077</v>
+        <v>0.5099046221570066</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="N15" s="5">
         <f>MAX(N2:N11)</f>
-        <v>0.91969768540387342</v>
+        <v>0.917693661971831</v>
       </c>
       <c r="O15" s="5">
         <f>MAX(O2:O11)</f>
@@ -2911,8 +3635,8 @@
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>73</v>
+      <c r="A20" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2922,13 +3646,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0461E122-F856-4AEC-9E32-871679C51D1A}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="14" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2968,13 +3692,25 @@
       <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>4783</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -3011,13 +3747,29 @@
         <f>F2/4089</f>
         <v>0.85595500122279289</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>I2/(I2+J2)</f>
+        <v>0.88165531163260158</v>
+      </c>
+      <c r="R2">
+        <f>I2/4067</f>
+        <v>0.85910990902385054</v>
+      </c>
+      <c r="T2">
+        <f>H2/(H2+K2)</f>
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="U2">
+        <f>H2/23</f>
+        <v>0.2608695652173913</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>4783</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3">
         <v>0</v>
@@ -3054,56 +3806,88 @@
         <f t="shared" ref="O3:O11" si="1">F3/4089</f>
         <v>0.90022010271460018</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">I3/(I3+J3)</f>
+        <v>0.87505949547834361</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">I3/4067</f>
+        <v>0.90410622080157366</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">H3/(H3+K3)</f>
+        <v>0.5</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">H3/23</f>
+        <v>0.17391304347826086</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>4783</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>4031</v>
-      </c>
-      <c r="E4" s="3">
-        <v>752</v>
-      </c>
-      <c r="F4" s="3">
-        <v>3544</v>
-      </c>
-      <c r="G4" s="3">
-        <v>487</v>
-      </c>
-      <c r="H4" s="3">
-        <v>6</v>
-      </c>
-      <c r="I4" s="3">
-        <v>3538</v>
-      </c>
-      <c r="J4" s="3">
-        <v>482</v>
-      </c>
-      <c r="K4" s="3">
-        <v>5</v>
+      <c r="B4">
+        <v>0.90027179594396822</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>3979</v>
+      </c>
+      <c r="E4">
+        <v>804</v>
+      </c>
+      <c r="F4">
+        <v>3502</v>
+      </c>
+      <c r="G4">
+        <v>477</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>3500</v>
+      </c>
+      <c r="J4">
+        <v>473</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
       </c>
       <c r="N4" s="3">
         <f t="shared" si="0"/>
-        <v>0.87918630612751181</v>
+        <v>0.88012063332495605</v>
       </c>
       <c r="O4" s="5">
         <f t="shared" si="1"/>
-        <v>0.8667155783810222</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.85644411836634871</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.88094638811980874</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.86058519793459554</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>8.6956521739130432E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4783</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C5" s="3">
         <v>0</v>
@@ -3140,13 +3924,29 @@
         <f t="shared" si="1"/>
         <v>0.8077769625825385</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.89002695417789757</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.81190066388000981</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>4783</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C6" s="3">
         <v>0</v>
@@ -3183,13 +3983,29 @@
         <f t="shared" si="1"/>
         <v>0.93176815847395456</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.86908841672378345</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.93533316941234323</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.2608695652173913</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>4783</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C7" s="3">
         <v>0</v>
@@ -3226,142 +4042,206 @@
         <f t="shared" si="1"/>
         <v>0.87649792125213988</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.87788131436978911</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.88025571674452918</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.17391304347826086</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>4783</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3">
-        <v>4188</v>
-      </c>
-      <c r="E8" s="3">
-        <v>595</v>
-      </c>
-      <c r="F8" s="3">
-        <v>3666</v>
-      </c>
-      <c r="G8" s="3">
-        <v>522</v>
-      </c>
-      <c r="H8" s="3">
-        <v>6</v>
-      </c>
-      <c r="I8" s="3">
-        <v>3660</v>
-      </c>
-      <c r="J8" s="3">
-        <v>517</v>
-      </c>
-      <c r="K8" s="3">
-        <v>5</v>
+      <c r="B8">
+        <v>0.90298975538365045</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>3942</v>
+      </c>
+      <c r="E8">
+        <v>841</v>
+      </c>
+      <c r="F8">
+        <v>3478</v>
+      </c>
+      <c r="G8">
+        <v>464</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>3477</v>
+      </c>
+      <c r="J8">
+        <v>461</v>
+      </c>
+      <c r="K8">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <f t="shared" si="0"/>
-        <v>0.87535816618911177</v>
+        <v>0.88229325215626586</v>
       </c>
       <c r="O8" s="5">
         <f t="shared" si="1"/>
-        <v>0.89655172413793105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+        <v>0.85057471264367812</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.88293550025393597</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.8549299237767396</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>4783</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="3">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3">
-        <v>3846</v>
-      </c>
-      <c r="E9" s="3">
-        <v>937</v>
-      </c>
-      <c r="F9" s="3">
-        <v>3402</v>
-      </c>
-      <c r="G9" s="3">
-        <v>444</v>
-      </c>
-      <c r="H9" s="3">
-        <v>4</v>
-      </c>
-      <c r="I9" s="3">
-        <v>3398</v>
-      </c>
-      <c r="J9" s="3">
-        <v>440</v>
-      </c>
-      <c r="K9" s="3">
-        <v>4</v>
+      <c r="B9">
+        <v>0.89650846748902357</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>4067</v>
+      </c>
+      <c r="E9">
+        <v>716</v>
+      </c>
+      <c r="F9">
+        <v>3572</v>
+      </c>
+      <c r="G9">
+        <v>495</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>3571</v>
+      </c>
+      <c r="J9">
+        <v>492</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
       </c>
       <c r="N9" s="3">
         <f t="shared" si="0"/>
-        <v>0.88455538221528862</v>
+        <v>0.87828866486353574</v>
       </c>
       <c r="O9" s="5">
         <f t="shared" si="1"/>
-        <v>0.83198826118855462</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
+        <v>0.87356321839080464</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.87890721142013295</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.87804278337841157</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>4783</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" s="3">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3">
-        <v>3922</v>
-      </c>
-      <c r="E10" s="3">
-        <v>861</v>
-      </c>
-      <c r="F10" s="3">
-        <v>3458</v>
-      </c>
-      <c r="G10" s="3">
-        <v>464</v>
-      </c>
-      <c r="H10" s="3">
-        <v>6</v>
-      </c>
-      <c r="I10" s="3">
-        <v>3452</v>
-      </c>
-      <c r="J10" s="3">
-        <v>458</v>
-      </c>
-      <c r="K10" s="3">
-        <v>6</v>
+      <c r="B10">
+        <v>0.88919088438218696</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>4211</v>
+      </c>
+      <c r="E10">
+        <v>572</v>
+      </c>
+      <c r="F10">
+        <v>3681</v>
+      </c>
+      <c r="G10">
+        <v>530</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>3680</v>
+      </c>
+      <c r="J10">
+        <v>528</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
       </c>
       <c r="N10" s="3">
         <f t="shared" si="0"/>
-        <v>0.88169301376848541</v>
+        <v>0.87413915934457376</v>
       </c>
       <c r="O10" s="5">
         <f t="shared" si="1"/>
-        <v>0.84568354120811939</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.90022010271460018</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.87452471482889738</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.90484386525694616</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>4783</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C11" s="3">
         <v>0</v>
@@ -3398,66 +4278,94 @@
         <f t="shared" si="1"/>
         <v>0.83125458547322084</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0.88543841336116913</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>0.83427587902630929</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.2608695652173913</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="D12" s="6">
         <f>AVERAGE(D2:D11)</f>
-        <v>4020.5</v>
+        <v>4041.7</v>
       </c>
       <c r="F12" s="6">
         <f>AVERAGE(F2:F11)</f>
-        <v>3534.7</v>
+        <v>3551</v>
       </c>
       <c r="H12" s="6">
         <f>AVERAGE(H2:H11)</f>
-        <v>4.9000000000000004</v>
+        <v>3.2</v>
       </c>
       <c r="I12" s="6">
         <f>AVERAGE(I2:I11)</f>
-        <v>3529.8</v>
+        <v>3547.8</v>
       </c>
       <c r="N12" s="6">
         <f>AVERAGE(N2:N11)</f>
-        <v>0.87944450024330578</v>
+        <v>0.87884938438219906</v>
       </c>
       <c r="O12" s="6">
         <f>AVERAGE(O2:O11)</f>
-        <v>0.86444118366348754</v>
+        <v>0.86842748838346806</v>
       </c>
       <c r="P12" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H13">
-        <f>H12+J13</f>
-        <v>485.79999999999995</v>
-      </c>
+      <c r="Q12" s="6">
+        <f t="shared" ref="Q12:R12" si="6">AVERAGE(Q2:Q11)</f>
+        <v>0.87964637203663598</v>
+      </c>
+      <c r="R12" s="6">
+        <f t="shared" si="6"/>
+        <v>0.87233833292353091</v>
+      </c>
+      <c r="T12" s="6">
+        <f t="shared" ref="T12:U12" si="7">AVERAGE(T2:T11)</f>
+        <v>0.39236596736596735</v>
+      </c>
+      <c r="U12" s="6">
+        <f t="shared" si="7"/>
+        <v>0.1391304347826087</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="I13">
-        <f>I12+K13</f>
-        <v>3534.7000000000003</v>
+        <f>I12+J13</f>
+        <v>4034.4</v>
       </c>
       <c r="J13" s="6">
         <f>AVERAGE(J2:J11)</f>
-        <v>480.9</v>
+        <v>486.6</v>
       </c>
       <c r="K13" s="6">
         <f>AVERAGE(K2:K11)</f>
-        <v>4.9000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N13" s="5">
         <f>STDEV(N2:N11)</f>
-        <v>6.0753009014232855E-3</v>
+        <v>5.9512400535829992E-3</v>
       </c>
       <c r="O13" s="5">
         <f>STDEV(O2:O11)</f>
-        <v>3.7688663279243903E-2</v>
+        <v>3.6214308765372447E-2</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="N14" s="5">
         <f>MIN(N2:N11)</f>
         <v>0.86807928913192067</v>
@@ -3470,7 +4378,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="N15" s="5">
         <f>MAX(N2:N11)</f>
         <v>0.88933764135702742</v>
@@ -3490,13 +4398,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{119E581A-AAC7-4DD6-8F2A-8A2BEA145347}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="14" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3536,56 +4444,84 @@
       <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+      <c r="Q1" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>4783</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3">
-        <v>4753</v>
-      </c>
-      <c r="E2" s="3">
-        <v>30</v>
-      </c>
-      <c r="F2" s="3">
-        <v>4060</v>
-      </c>
-      <c r="G2" s="3">
-        <v>693</v>
-      </c>
-      <c r="H2" s="3">
-        <v>32</v>
-      </c>
-      <c r="I2" s="3">
-        <v>4028</v>
-      </c>
-      <c r="J2" s="3">
-        <v>652</v>
-      </c>
-      <c r="K2" s="3">
-        <v>41</v>
+      <c r="B2">
+        <v>0.83274095755801802</v>
+      </c>
+      <c r="C2">
+        <v>159</v>
+      </c>
+      <c r="D2">
+        <v>4624</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>3983</v>
+      </c>
+      <c r="G2">
+        <v>641</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>3977</v>
+      </c>
+      <c r="J2">
+        <v>634</v>
+      </c>
+      <c r="K2">
+        <v>7</v>
       </c>
       <c r="N2" s="3">
         <f>F2/D2</f>
-        <v>0.85419734904270983</v>
+        <v>0.86137543252595161</v>
       </c>
       <c r="O2" s="5">
         <f>F2/4089</f>
-        <v>0.99290780141843971</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.97407679139153824</v>
+      </c>
+      <c r="Q2">
+        <f>I2/(I2+J2)</f>
+        <v>0.86250271090869657</v>
+      </c>
+      <c r="R2">
+        <f>I2/4067</f>
+        <v>0.97787066633882469</v>
+      </c>
+      <c r="T2">
+        <f>H2/(H2+K2)</f>
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="U2">
+        <f t="shared" ref="U2:U11" si="0">H2/23</f>
+        <v>0.2608695652173913</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>4783</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3">
         <v>0</v>
@@ -3615,20 +4551,36 @@
         <v>10</v>
       </c>
       <c r="N3" s="3">
-        <f t="shared" ref="N3:N11" si="0">F3/D3</f>
+        <f t="shared" ref="N3:N11" si="1">F3/D3</f>
         <v>0.85804950285593395</v>
       </c>
       <c r="O3" s="5">
-        <f t="shared" ref="O3:O11" si="1">F3/4089</f>
+        <f t="shared" ref="O3:O11" si="2">F3/4089</f>
         <v>0.99192956713132796</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="3">I3/(I3+J3)</f>
+        <v>0.85948129251700678</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="4">I3/4067</f>
+        <v>0.9940988443570199</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="5">H3/(H3+K3)</f>
+        <v>0.56521739130434778</v>
+      </c>
+      <c r="U3">
+        <f t="shared" si="0"/>
+        <v>0.56521739130434778</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>4783</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3">
         <v>0</v>
@@ -3658,20 +4610,36 @@
         <v>11</v>
       </c>
       <c r="N4" s="3">
+        <f t="shared" si="1"/>
+        <v>0.85976520811099255</v>
+      </c>
+      <c r="O4" s="5">
+        <f t="shared" si="2"/>
+        <v>0.98508192712154563</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="3"/>
+        <v>0.86131386861313863</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="4"/>
+        <v>0.98647651831817063</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="5"/>
+        <v>0.59259259259259256</v>
+      </c>
+      <c r="U4">
         <f t="shared" si="0"/>
-        <v>0.85976520811099255</v>
-      </c>
-      <c r="O4" s="5">
-        <f t="shared" si="1"/>
-        <v>0.98508192712154563</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.69565217391304346</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>4783</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C5" s="3">
         <v>88</v>
@@ -3701,63 +4669,95 @@
         <v>8</v>
       </c>
       <c r="N5" s="3">
+        <f t="shared" si="1"/>
+        <v>0.85942492012779548</v>
+      </c>
+      <c r="O5" s="5">
+        <f t="shared" si="2"/>
+        <v>0.98679383712399116</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="3"/>
+        <v>0.86068376068376073</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="4"/>
+        <v>0.9904106220801574</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="5"/>
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="U5">
         <f t="shared" si="0"/>
-        <v>0.85942492012779548</v>
-      </c>
-      <c r="O5" s="5">
+        <v>0.30434782608695654</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4783</v>
+      </c>
+      <c r="B6">
+        <v>0.86326573280367969</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>4661</v>
+      </c>
+      <c r="E6">
+        <v>122</v>
+      </c>
+      <c r="F6">
+        <v>4007</v>
+      </c>
+      <c r="G6">
+        <v>654</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>3998</v>
+      </c>
+      <c r="J6">
+        <v>645</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="N6" s="3">
         <f t="shared" si="1"/>
-        <v>0.98679383712399116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <v>4783</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="3">
-        <v>5</v>
-      </c>
-      <c r="D6" s="3">
-        <v>4778</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>4085</v>
-      </c>
-      <c r="G6" s="3">
-        <v>693</v>
-      </c>
-      <c r="H6" s="3">
-        <v>24</v>
-      </c>
-      <c r="I6" s="3">
-        <v>4061</v>
-      </c>
-      <c r="J6" s="3">
-        <v>669</v>
-      </c>
-      <c r="K6" s="3">
-        <v>24</v>
-      </c>
-      <c r="N6" s="3">
-        <f t="shared" si="0"/>
-        <v>0.85496023440770197</v>
+        <v>0.85968676249731812</v>
       </c>
       <c r="O6" s="5">
-        <f t="shared" si="1"/>
-        <v>0.99902176571288825</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>0.97994619711420883</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="3"/>
+        <v>0.86108119750161538</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="4"/>
+        <v>0.9830341775264323</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="U6">
+        <f>H6/33</f>
+        <v>0.27272727272727271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>4783</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C7" s="3">
         <v>159</v>
@@ -3787,20 +4787,36 @@
         <v>7</v>
       </c>
       <c r="N7" s="3">
+        <f t="shared" si="1"/>
+        <v>0.86137543252595161</v>
+      </c>
+      <c r="O7" s="5">
+        <f t="shared" si="2"/>
+        <v>0.97407679139153824</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="3"/>
+        <v>0.86250271090869657</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="4"/>
+        <v>0.97787066633882469</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="5"/>
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="U7">
         <f t="shared" si="0"/>
-        <v>0.86137543252595161</v>
-      </c>
-      <c r="O7" s="5">
-        <f t="shared" si="1"/>
-        <v>0.97407679139153824</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.2608695652173913</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>4783</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C8" s="3">
         <v>123</v>
@@ -3830,20 +4846,36 @@
         <v>11</v>
       </c>
       <c r="N8" s="3">
+        <f t="shared" si="1"/>
+        <v>0.85965665236051503</v>
+      </c>
+      <c r="O8" s="5">
+        <f t="shared" si="2"/>
+        <v>0.97970163854243086</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="3"/>
+        <v>0.86127292340884576</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="4"/>
+        <v>0.98155888861568719</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="5"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="U8">
         <f t="shared" si="0"/>
-        <v>0.85965665236051503</v>
-      </c>
-      <c r="O8" s="5">
-        <f t="shared" si="1"/>
-        <v>0.97970163854243086</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.60869565217391308</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>4783</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C9" s="3">
         <v>0</v>
@@ -3873,20 +4905,36 @@
         <v>13</v>
       </c>
       <c r="N9" s="3">
+        <f t="shared" si="1"/>
+        <v>0.85717295133768701</v>
+      </c>
+      <c r="O9" s="5">
+        <f t="shared" si="2"/>
+        <v>0.99510882856444116</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="3"/>
+        <v>0.85893084429359357</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="4"/>
+        <v>0.99557413326776489</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="5"/>
+        <v>0.60606060606060608</v>
+      </c>
+      <c r="U9">
         <f t="shared" si="0"/>
-        <v>0.85717295133768701</v>
-      </c>
-      <c r="O9" s="5">
-        <f t="shared" si="1"/>
-        <v>0.99510882856444116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.86956521739130432</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>4783</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C10" s="3">
         <v>0</v>
@@ -3904,7 +4952,7 @@
         <v>705</v>
       </c>
       <c r="H10" s="3">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I10" s="3">
         <v>4045</v>
@@ -3916,20 +4964,36 @@
         <v>43</v>
       </c>
       <c r="N10" s="3">
+        <f t="shared" si="1"/>
+        <v>0.85260296884800335</v>
+      </c>
+      <c r="O10" s="5">
+        <f t="shared" si="2"/>
+        <v>0.99730985571044262</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="3"/>
+        <v>0.85935840237943484</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="4"/>
+        <v>0.99459060732726823</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="5"/>
+        <v>0.33846153846153848</v>
+      </c>
+      <c r="U10">
         <f t="shared" si="0"/>
-        <v>0.85260296884800335</v>
-      </c>
-      <c r="O10" s="5">
-        <f t="shared" si="1"/>
-        <v>0.99730985571044262</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.95652173913043481</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>4783</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C11" s="3">
         <v>0</v>
@@ -3959,74 +5023,102 @@
         <v>12</v>
       </c>
       <c r="N11" s="3">
+        <f t="shared" si="1"/>
+        <v>0.86087144089732526</v>
+      </c>
+      <c r="O11" s="5">
+        <f t="shared" si="2"/>
+        <v>0.97603325996576185</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="3"/>
+        <v>0.86263020833333337</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="4"/>
+        <v>0.97737890336857636</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="5"/>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="U11">
         <f t="shared" si="0"/>
-        <v>0.86087144089732526</v>
-      </c>
-      <c r="O11" s="5">
-        <f t="shared" si="1"/>
-        <v>0.97603325996576185</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.69565217391304346</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="D12" s="6">
         <f>AVERAGE(D2:D11)</f>
-        <v>4708.8</v>
+        <v>4684.2</v>
       </c>
       <c r="F12" s="6">
         <f>AVERAGE(F2:F11)</f>
-        <v>4039.1</v>
+        <v>4023.6</v>
       </c>
       <c r="H12" s="6">
         <f>AVERAGE(H2:H11)</f>
-        <v>18.100000000000001</v>
+        <v>12.9</v>
       </c>
       <c r="I12" s="6">
         <f>AVERAGE(I2:I11)</f>
-        <v>4021</v>
+        <v>4009.6</v>
       </c>
       <c r="N12" s="6">
         <f>AVERAGE(N2:N11)</f>
-        <v>0.85780766605146164</v>
+        <v>0.85899812720874746</v>
       </c>
       <c r="O12" s="6">
         <f>AVERAGE(O2:O11)</f>
-        <v>0.98779652726828071</v>
+        <v>0.98400586940572266</v>
       </c>
       <c r="P12" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q12" s="6">
+        <f t="shared" ref="Q12:R12" si="6">AVERAGE(Q2:Q11)</f>
+        <v>0.86097579195481211</v>
+      </c>
+      <c r="R12" s="6">
+        <f t="shared" si="6"/>
+        <v>0.98588640275387274</v>
+      </c>
+      <c r="T12" s="6">
+        <f t="shared" ref="T12:U12" si="7">AVERAGE(T2:T11)</f>
+        <v>0.51235042895912453</v>
+      </c>
+      <c r="U12" s="6">
+        <f t="shared" si="7"/>
+        <v>0.54901185770750982</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G13" s="6"/>
-      <c r="H13">
-        <f>H12+J13</f>
-        <v>669.80000000000007</v>
-      </c>
       <c r="I13">
-        <f>I12+K13</f>
-        <v>4039</v>
+        <f>I12+J13</f>
+        <v>4657.1000000000004</v>
       </c>
       <c r="J13" s="6">
         <f>AVERAGE(J2:J11)</f>
-        <v>651.70000000000005</v>
+        <v>647.5</v>
       </c>
       <c r="K13" s="6">
         <f>AVERAGE(K2:K11)</f>
-        <v>18</v>
+        <v>13.1</v>
       </c>
       <c r="N13" s="5">
         <f>STDEV(N2:N11)</f>
-        <v>2.9939639761265499E-3</v>
+        <v>2.6166159261065214E-3</v>
       </c>
       <c r="O13" s="5">
         <f>STDEV(O2:O11)</f>
-        <v>8.9050145891968416E-3</v>
+        <v>8.6134934690588229E-3</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="N14" s="5">
         <f>MIN(N2:N11)</f>
         <v>0.85260296884800335</v>
@@ -4039,14 +5131,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="N15" s="5">
         <f>MAX(N2:N11)</f>
         <v>0.86137543252595161</v>
       </c>
       <c r="O15" s="5">
         <f>MAX(O2:O11)</f>
-        <v>0.99902176571288825</v>
+        <v>0.99730985571044262</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>16</v>
